--- a/data/trans_dic/IP04D$individual-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$individual-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,37; 31,0</t>
+          <t>18,5; 31,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,28; 38,73</t>
+          <t>25,02; 38,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,87; 24,23</t>
+          <t>12,11; 24,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,55; 36,04</t>
+          <t>23,12; 35,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,92; 29,55</t>
+          <t>18,0; 29,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,94; 48,26</t>
+          <t>19,95; 45,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,31; 31,44</t>
+          <t>22,66; 31,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,95; 31,75</t>
+          <t>22,7; 31,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,11; 34,96</t>
+          <t>17,82; 34,59</t>
         </is>
       </c>
     </row>
@@ -785,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,82; 33,59</t>
+          <t>23,29; 33,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,94; 36,26</t>
+          <t>25,74; 35,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,84; 20,66</t>
+          <t>11,35; 20,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,97; 32,84</t>
+          <t>23,09; 32,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,21; 34,59</t>
+          <t>24,94; 34,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,21; 23,34</t>
+          <t>13,29; 22,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,87; 32,01</t>
+          <t>24,84; 32,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,66; 33,75</t>
+          <t>26,6; 33,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,09; 20,21</t>
+          <t>13,59; 20,21</t>
         </is>
       </c>
     </row>
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,32; 26,71</t>
+          <t>16,57; 26,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,84; 41,75</t>
+          <t>30,41; 41,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,33</t>
+          <t>1,86; 7,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,55; 32,04</t>
+          <t>21,48; 32,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,49; 39,9</t>
+          <t>28,3; 40,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,94; 19,63</t>
+          <t>8,18; 19,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,48; 27,92</t>
+          <t>20,4; 27,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,46; 39,04</t>
+          <t>30,59; 39,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 12,17</t>
+          <t>5,36; 12,26</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,82; 40,68</t>
+          <t>29,88; 41,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,77; 35,55</t>
+          <t>24,07; 35,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,48; 35,17</t>
+          <t>23,89; 35,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,1; 47,46</t>
+          <t>35,77; 47,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,3; 32,1</t>
+          <t>22,15; 31,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,26; 33,16</t>
+          <t>21,21; 33,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,32; 42,08</t>
+          <t>34,31; 42,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,14; 32,57</t>
+          <t>25,15; 32,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,27; 32,6</t>
+          <t>24,01; 32,15</t>
         </is>
       </c>
     </row>
@@ -1115,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,48; 30,94</t>
+          <t>25,65; 31,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,96; 34,57</t>
+          <t>28,87; 34,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,62; 18,88</t>
+          <t>13,14; 18,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,13; 34,51</t>
+          <t>28,85; 34,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,08; 31,18</t>
+          <t>25,72; 31,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,69; 24,76</t>
+          <t>17,63; 25,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,0; 32,0</t>
+          <t>27,92; 31,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,25; 32,25</t>
+          <t>28,46; 32,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,39; 21,11</t>
+          <t>16,44; 21,29</t>
         </is>
       </c>
     </row>
@@ -1180,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>33891</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>41477</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20571</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>45403</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35089</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>40182</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>79294</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>76565</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>60753</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>25603; 43501</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>33244; 51331</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14198; 28680</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>35756; 54743</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>26655; 43684</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>28011; 64480</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>66396; 93341</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>63773; 88825</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>45928; 89137</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>58754</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>63303</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30044</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>62435</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66193</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>45192</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>121189</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>129496</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>75236</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>47750; 68130</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>53014; 73570</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>21506; 38854</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>51691; 73677</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>55786; 77609</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>33805; 57473</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>106523; 137664</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>114294; 142895</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>60321; 89692</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>33361</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>56124</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7696</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43753</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>56231</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22554</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>77115</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>112355</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>30250</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>25746; 41362</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>47446; 65397</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3534; 13375</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35515; 54001</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>46961; 67289</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>15160; 36199</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>65419; 88906</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>98458; 126891</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>20133; 46063</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>73902</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>61841</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>49121</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>86430</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54526</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>48387</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>160332</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>116367</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>97509</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>62598; 85978</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49428; 72886</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>40122; 60183</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>74535; 98422</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>44810; 64370</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>38239; 60126</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>143383; 177666</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>102537; 132983</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>83613; 111975</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>199908</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>222745</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>107431</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>238021</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>212039</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>156315</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>437929</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>434784</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>263747</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>181701; 221031</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>202173; 242461</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>87393; 123999</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>217052; 258778</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>190319; 232392</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>134069; 191362</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>407801; 466932</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>409889; 465742</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>234280; 303437</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$individual-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$individual-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,5; 31,43</t>
+          <t>18,43; 31,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,02; 38,63</t>
+          <t>24,21; 38,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,11; 24,45</t>
+          <t>12,04; 24,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,12; 35,39</t>
+          <t>23,08; 36,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,0; 29,5</t>
+          <t>18,0; 29,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,95; 45,92</t>
+          <t>19,29; 47,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,66; 31,85</t>
+          <t>22,9; 31,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,7; 31,62</t>
+          <t>23,19; 32,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,82; 34,59</t>
+          <t>18,21; 35,27</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,29; 33,23</t>
+          <t>24,01; 33,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,74; 35,72</t>
+          <t>26,41; 35,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,35; 20,5</t>
+          <t>11,42; 20,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,09; 32,92</t>
+          <t>23,12; 33,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,94; 34,7</t>
+          <t>24,89; 35,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,29; 22,6</t>
+          <t>13,35; 22,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,84; 32,1</t>
+          <t>25,36; 32,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,6; 33,26</t>
+          <t>26,81; 33,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,59; 20,21</t>
+          <t>13,84; 20,67</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,57; 26,62</t>
+          <t>16,52; 27,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,41; 41,92</t>
+          <t>30,28; 42,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,02</t>
+          <t>1,89; 7,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,48; 32,67</t>
+          <t>21,9; 32,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,3; 40,56</t>
+          <t>28,54; 40,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,18; 19,54</t>
+          <t>7,52; 19,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,4; 27,72</t>
+          <t>20,41; 28,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,59; 39,42</t>
+          <t>30,52; 39,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 12,26</t>
+          <t>5,61; 12,68</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,88; 41,04</t>
+          <t>29,9; 41,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,07; 35,5</t>
+          <t>25,17; 35,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,89; 35,83</t>
+          <t>23,13; 35,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,77; 47,23</t>
+          <t>35,59; 47,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,15; 31,81</t>
+          <t>21,66; 31,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,21; 33,35</t>
+          <t>21,11; 33,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,31; 42,51</t>
+          <t>34,18; 42,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,15; 32,62</t>
+          <t>24,67; 32,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,01; 32,15</t>
+          <t>24,28; 32,9</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,65; 31,21</t>
+          <t>25,4; 31,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,87; 34,63</t>
+          <t>29,0; 34,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,14; 18,64</t>
+          <t>13,43; 19,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,85; 34,4</t>
+          <t>28,9; 34,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,72; 31,4</t>
+          <t>26,14; 31,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,63; 25,17</t>
+          <t>17,7; 24,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,92; 31,97</t>
+          <t>28,01; 32,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,46; 32,34</t>
+          <t>28,13; 32,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,44; 21,29</t>
+          <t>16,32; 21,11</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25603; 43501</t>
+          <t>25499; 42949</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33244; 51331</t>
+          <t>32168; 50535</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14198; 28680</t>
+          <t>14119; 28925</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35756; 54743</t>
+          <t>35706; 55911</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26655; 43684</t>
+          <t>26656; 44297</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28011; 64480</t>
+          <t>27090; 66005</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66396; 93341</t>
+          <t>67113; 92105</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>63773; 88825</t>
+          <t>65160; 91939</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45928; 89137</t>
+          <t>46921; 90895</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47750; 68130</t>
+          <t>49216; 69636</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53014; 73570</t>
+          <t>54401; 73483</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21506; 38854</t>
+          <t>21634; 39346</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51691; 73677</t>
+          <t>51759; 73919</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55786; 77609</t>
+          <t>55684; 78364</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33805; 57473</t>
+          <t>33944; 57464</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>106523; 137664</t>
+          <t>108774; 138121</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>114294; 142895</t>
+          <t>115174; 145938</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60321; 89692</t>
+          <t>61432; 91757</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25746; 41362</t>
+          <t>25665; 41987</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47446; 65397</t>
+          <t>47243; 65827</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3534; 13375</t>
+          <t>3595; 13493</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35515; 54001</t>
+          <t>36203; 53948</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46961; 67289</t>
+          <t>47358; 67550</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15160; 36199</t>
+          <t>13939; 35972</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65419; 88906</t>
+          <t>65449; 90848</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>98458; 126891</t>
+          <t>98262; 125943</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20133; 46063</t>
+          <t>21066; 47643</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62598; 85978</t>
+          <t>62646; 86485</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49428; 72886</t>
+          <t>51681; 73558</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40122; 60183</t>
+          <t>38858; 59611</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74535; 98422</t>
+          <t>74177; 98750</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44810; 64370</t>
+          <t>43827; 64405</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38239; 60126</t>
+          <t>38058; 60058</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>143383; 177666</t>
+          <t>142834; 177136</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>102537; 132983</t>
+          <t>100581; 131265</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>83613; 111975</t>
+          <t>84547; 114585</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>181701; 221031</t>
+          <t>179896; 219776</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202173; 242461</t>
+          <t>203027; 242223</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87393; 123999</t>
+          <t>89346; 126675</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>217052; 258778</t>
+          <t>217360; 259166</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>190319; 232392</t>
+          <t>193406; 234009</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>134069; 191362</t>
+          <t>134546; 189991</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>407801; 466932</t>
+          <t>409122; 467887</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>409889; 465742</t>
+          <t>405192; 463161</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>234280; 303437</t>
+          <t>232576; 300917</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$individual-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$individual-Habitat-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción individual en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29,35%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23,7%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28,77%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>24,49%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>31,22%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29,35%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,7%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,43; 31,04</t>
+          <t>23,55; 36,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,21; 38,03</t>
+          <t>17,92; 29,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,04; 24,66</t>
+          <t>20,19; 45,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,08; 36,15</t>
+          <t>18,37; 31,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,0; 29,92</t>
+          <t>24,28; 38,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,29; 47,01</t>
+          <t>12,33; 23,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,9; 31,43</t>
+          <t>23,31; 31,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,19; 32,72</t>
+          <t>22,95; 31,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,21; 35,27</t>
+          <t>17,95; 32,4</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>27,89%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29,59%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17,23%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>28,66%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>30,73%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15,85%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>29,59%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,01; 33,97</t>
+          <t>22,97; 32,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,41; 35,68</t>
+          <t>25,21; 34,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,42; 20,76</t>
+          <t>12,93; 22,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,12; 33,02</t>
+          <t>23,82; 33,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,89; 35,03</t>
+          <t>25,94; 36,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,35; 22,59</t>
+          <t>12,49; 22,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,36; 32,21</t>
+          <t>24,87; 32,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,81; 33,97</t>
+          <t>26,66; 33,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,84; 20,67</t>
+          <t>14,0; 20,36</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26,47%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33,89%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,83%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>21,47%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>35,98%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26,47%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>33,89%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,52; 27,02</t>
+          <t>21,55; 32,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,28; 42,2</t>
+          <t>27,49; 39,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,09</t>
+          <t>8,28; 20,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,9; 32,63</t>
+          <t>16,32; 26,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,54; 40,71</t>
+          <t>29,84; 41,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,52; 19,41</t>
+          <t>2,54; 8,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,41; 28,33</t>
+          <t>20,48; 27,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,52; 39,12</t>
+          <t>30,46; 39,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 12,68</t>
+          <t>6,1; 13,26</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41,47%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26,95%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26,92%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>35,27%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>30,12%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29,25%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41,47%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>26,95%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,9; 41,28</t>
+          <t>36,1; 47,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,17; 35,82</t>
+          <t>22,3; 32,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,13; 35,49</t>
+          <t>21,45; 33,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,59; 47,39</t>
+          <t>29,82; 40,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,66; 31,83</t>
+          <t>24,77; 35,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,11; 33,31</t>
+          <t>23,17; 34,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,18; 42,39</t>
+          <t>34,32; 42,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,67; 32,2</t>
+          <t>25,14; 32,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,28; 32,9</t>
+          <t>24,05; 32,48</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>31,64%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28,65%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20,58%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>28,22%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>31,81%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>16,15%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>31,64%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>28,65%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,4; 31,03</t>
+          <t>29,13; 34,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,0; 34,59</t>
+          <t>26,08; 31,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,43; 19,04</t>
+          <t>17,68; 24,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,9; 34,45</t>
+          <t>25,48; 30,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,14; 31,62</t>
+          <t>28,96; 34,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,7; 24,99</t>
+          <t>14,76; 19,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,01; 32,04</t>
+          <t>28,0; 32,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,13; 32,16</t>
+          <t>28,25; 32,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 21,11</t>
+          <t>16,88; 21,28</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción individual en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>45403</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35089</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36220</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>33891</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>41477</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20571</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>45403</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>35089</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40182</t>
+          <t>20724</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60753</t>
+          <t>56944</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25499; 42949</t>
+          <t>36435; 55751</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32168; 50535</t>
+          <t>26530; 43751</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14119; 28925</t>
+          <t>25420; 57909</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35706; 55911</t>
+          <t>25427; 42904</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26656; 44297</t>
+          <t>32255; 51463</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27090; 66005</t>
+          <t>14932; 28683</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>67113; 92105</t>
+          <t>68326; 92138</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>65160; 91939</t>
+          <t>64476; 89212</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46921; 90895</t>
+          <t>44329; 80017</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>62435</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>66193</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>40754</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>58754</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>63303</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>30044</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>62435</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>66193</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45192</t>
+          <t>30638</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>75236</t>
+          <t>71392</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49216; 69636</t>
+          <t>51406; 73498</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54401; 73483</t>
+          <t>56390; 77379</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21634; 39346</t>
+          <t>30580; 53379</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51759; 73919</t>
+          <t>48836; 68861</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55684; 78364</t>
+          <t>53424; 74681</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33944; 57464</t>
+          <t>22891; 40552</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>108774; 138121</t>
+          <t>106662; 137291</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>115174; 145938</t>
+          <t>114543; 145031</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61432; 91757</t>
+          <t>58797; 85478</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>43753</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>56231</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>21599</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>33361</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>56124</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7696</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>43753</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>56231</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22554</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30250</t>
+          <t>28865</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25665; 41987</t>
+          <t>35624; 52971</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47243; 65827</t>
+          <t>45608; 66198</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3595; 13493</t>
+          <t>13935; 35112</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36203; 53948</t>
+          <t>25363; 41509</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>47358; 67550</t>
+          <t>46548; 65126</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13939; 35972</t>
+          <t>3994; 12968</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65449; 90848</t>
+          <t>65676; 89536</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>98262; 125943</t>
+          <t>98068; 125666</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21066; 47643</t>
+          <t>19865; 43135</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>86430</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>54526</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>45346</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>73902</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>61841</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>49121</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>86430</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>54526</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48387</t>
+          <t>48231</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>97509</t>
+          <t>93577</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62646; 86485</t>
+          <t>75232; 98895</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51681; 73558</t>
+          <t>45115; 64953</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38858; 59611</t>
+          <t>36119; 56150</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74177; 98750</t>
+          <t>62476; 85231</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43827; 64405</t>
+          <t>50851; 72997</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38058; 60058</t>
+          <t>38731; 58277</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>142834; 177136</t>
+          <t>143429; 175866</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100581; 131265</t>
+          <t>102479; 132785</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84547; 114585</t>
+          <t>80708; 109002</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>287</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>342</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>154</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>238021</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>212039</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>143920</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>199908</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>222745</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>107431</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>238021</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>212039</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>156315</t>
+          <t>106858</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>263747</t>
+          <t>250778</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>179896; 219776</t>
+          <t>219149; 259581</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>203027; 242223</t>
+          <t>193026; 230708</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89346; 126675</t>
+          <t>123615; 172157</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>217360; 259166</t>
+          <t>180444; 219171</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>193406; 234009</t>
+          <t>202777; 242038</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>134546; 189991</t>
+          <t>92798; 123777</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>409122; 467887</t>
+          <t>409018; 467293</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>405192; 463161</t>
+          <t>406858; 464447</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>232576; 300917</t>
+          <t>224131; 282524</t>
         </is>
       </c>
     </row>
